--- a/data/trans_dic/P36BPD07_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD07_R-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,92; 88,34</t>
+          <t>78,67; 87,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,27; 87,27</t>
+          <t>77,86; 87,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,68; 90,05</t>
+          <t>81,96; 89,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,34; 91,56</t>
+          <t>81,01; 89,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,71; 88,04</t>
+          <t>81,9; 87,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,21; 88,35</t>
+          <t>80,94; 87,11</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,46; 87,15</t>
+          <t>80,0; 86,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,67; 83,97</t>
+          <t>74,91; 83,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,92; 90,74</t>
+          <t>85,31; 90,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,66; 84,19</t>
+          <t>77,75; 84,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,72; 88,14</t>
+          <t>83,66; 88,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,37; 83,13</t>
+          <t>77,81; 83,28</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,16; 97,6</t>
+          <t>93,43; 97,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,08; 85,61</t>
+          <t>75,52; 84,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,45; 99,34</t>
+          <t>96,37; 99,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,91; 90,99</t>
+          <t>84,91; 90,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95,53; 98,14</t>
+          <t>95,57; 98,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,16; 87,27</t>
+          <t>81,69; 86,92</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,12; 82,92</t>
+          <t>73,86; 82,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,5; 88,43</t>
+          <t>76,58; 87,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,01; 87,46</t>
+          <t>80,21; 87,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83,76; 93,07</t>
+          <t>80,76; 88,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,45; 84,29</t>
+          <t>78,68; 84,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,7; 90,36</t>
+          <t>80,35; 86,94</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,23; 86,03</t>
+          <t>75,76; 86,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,59; 82,26</t>
+          <t>69,77; 80,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,59; 90,03</t>
+          <t>81,54; 90,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,21; 91,11</t>
+          <t>83,37; 90,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,77; 86,98</t>
+          <t>79,7; 86,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,31; 85,99</t>
+          <t>78,94; 85,14</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82,55; 90,78</t>
+          <t>81,98; 90,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,86; 89,22</t>
+          <t>81,43; 89,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,81; 94,21</t>
+          <t>87,15; 93,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89,44; 95,07</t>
+          <t>89,84; 94,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,02; 91,33</t>
+          <t>86,08; 91,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,61; 91,5</t>
+          <t>86,56; 91,34</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82,34; 88,2</t>
+          <t>82,25; 88,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74,37; 83,38</t>
+          <t>76,83; 83,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,69; 84,68</t>
+          <t>78,9; 84,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,68; 93,65</t>
+          <t>78,27; 84,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,32; 85,49</t>
+          <t>81,47; 85,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,71; 89,89</t>
+          <t>78,35; 83,11</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>78,9; 84,74</t>
+          <t>79,05; 84,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,0; 78,58</t>
+          <t>34,7; 42,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82,81; 87,58</t>
+          <t>82,4; 87,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43,21; 50,17</t>
+          <t>44,25; 50,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,71; 85,48</t>
+          <t>81,73; 85,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,74; 71,7</t>
+          <t>40,45; 45,11</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>83,09; 85,7</t>
+          <t>83,16; 85,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71,27; 79,78</t>
+          <t>69,74; 73,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85,58; 87,81</t>
+          <t>85,58; 87,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76,94; 82,6</t>
+          <t>74,95; 77,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>84,78; 86,46</t>
+          <t>84,7; 86,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74,64; 79,51</t>
+          <t>72,88; 75,07</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>255748</t>
+          <t>264352</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254405</t>
+          <t>271314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>510152</t>
+          <t>535666</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>231829; 259504</t>
+          <t>231104; 257985</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>231302; 271786</t>
+          <t>248265; 278099</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>235813; 259965</t>
+          <t>236626; 259653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>238480; 265183</t>
+          <t>256049; 281651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>475937; 512807</t>
+          <t>477039; 512223</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>482097; 531068</t>
+          <t>513885; 553074</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>412278</t>
+          <t>424194</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417076</t>
+          <t>443265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>829353</t>
+          <t>867459</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>404362; 438015</t>
+          <t>402081; 436756</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>387092; 435272</t>
+          <t>397483; 445686</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>442088; 472341</t>
+          <t>444092; 473065</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>398672; 432208</t>
+          <t>423725; 458378</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>856586; 901812</t>
+          <t>855932; 901499</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>798301; 857712</t>
+          <t>836879; 895731</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>255921</t>
+          <t>253037</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307526</t>
+          <t>313927</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>563447</t>
+          <t>566962</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>292468; 306412</t>
+          <t>293323; 306735</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>239802; 269840</t>
+          <t>237992; 266180</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>324363; 334088</t>
+          <t>324106; 333578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>295858; 317054</t>
+          <t>302014; 323150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>621208; 638195</t>
+          <t>621454; 637913</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>545230; 579146</t>
+          <t>548030; 583111</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>259999</t>
+          <t>309324</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>419891</t>
+          <t>356542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>679890</t>
+          <t>665866</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>274220; 306772</t>
+          <t>273269; 306440</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>239119; 276386</t>
+          <t>285742; 325955</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>307192; 335777</t>
+          <t>307977; 335878</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>397593; 441785</t>
+          <t>339894; 372076</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>591403; 635456</t>
+          <t>593152; 635624</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>651006; 711326</t>
+          <t>637977; 690342</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>137394</t>
+          <t>157058</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183578</t>
+          <t>197740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>320972</t>
+          <t>354798</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>158896; 181722</t>
+          <t>160022; 182332</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>126174; 147031</t>
+          <t>143493; 166508</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>176152; 196794</t>
+          <t>178227; 197467</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>175379; 189768</t>
+          <t>189108; 205204</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>342861; 373862</t>
+          <t>342555; 373390</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>306944; 332793</t>
+          <t>341404; 368224</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>230913</t>
+          <t>232116</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238647</t>
+          <t>244667</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>469560</t>
+          <t>476783</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>217217; 238850</t>
+          <t>215696; 238466</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>218017; 240564</t>
+          <t>220435; 241706</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>239823; 257289</t>
+          <t>238011; 256704</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>229918; 244381</t>
+          <t>236953; 250383</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>461282; 489759</t>
+          <t>461587; 491121</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>456154; 481926</t>
+          <t>462601; 488194</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>492227</t>
+          <t>577405</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>731023</t>
+          <t>625411</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1223250</t>
+          <t>1202817</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>529340; 566969</t>
+          <t>528727; 566716</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>462141; 518081</t>
+          <t>550530; 601477</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>531823; 572304</t>
+          <t>533231; 572996</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>684488; 794463</t>
+          <t>602609; 647457</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1072380; 1127386</t>
+          <t>1074303; 1129155</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1171536; 1321200</t>
+          <t>1164729; 1235494</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>507698</t>
+          <t>303518</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>334155</t>
+          <t>391555</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>841853</t>
+          <t>695072</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>610441; 655579</t>
+          <t>611619; 655180</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>343204; 728959</t>
+          <t>276501; 335830</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>683311; 722736</t>
+          <t>679957; 720965</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>309573; 359462</t>
+          <t>367209; 421598</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1306510; 1366733</t>
+          <t>1306780; 1368243</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>686210; 1178763</t>
+          <t>658004; 733849</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2552177</t>
+          <t>2521004</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2886300</t>
+          <t>2844420</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5438477</t>
+          <t>5365424</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2800989; 2889160</t>
+          <t>2803345; 2886551</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2462346; 2756369</t>
+          <t>2460119; 2583832</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3014471; 3093012</t>
+          <t>3014342; 3093238</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2813060; 3020270</t>
+          <t>2794219; 2894783</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5843895; 5960210</t>
+          <t>5838447; 5961622</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5307759; 5654380</t>
+          <t>5287905; 5446729</t>
         </is>
       </c>
     </row>
